--- a/banco/tb_uf.xlsx
+++ b/banco/tb_uf.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp_811_10-2022\htdocs\FNDE\banco\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mbs10065305\xampp_8_2\htdocs\fnde\banco\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>AL</t>
   </si>
@@ -192,6 +192,12 @@
   </si>
   <si>
     <t>SP</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>CORREIOS SEDE</t>
   </si>
 </sst>
 </file>
@@ -512,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" customWidth="1"/>
@@ -743,6 +749,14 @@
         <v>52</v>
       </c>
     </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
